--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0075.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0075.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Pop Gummy</t>
+          <t>Kẹo Dẻo Nổ</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Dried Berry Snack</t>
+          <t>Bữa Ăn Nhẹ Quả Mọng Khô</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Nutritious Breakfast</t>
+          <t>Bữa Sáng Bổ Dưỡng</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Enhanced Terminal</t>
+          <t>Thiết bị Đầu Cuối Nâng Cao</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Sliced Star</t>
+          <t>Ngôi Sao Bị Xẻ Đôi</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Watcher's Milk</t>
+          <t>Sữa Giám Thị</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>False Sovereign</t>
+          <t>Chúa tể giả hiệu</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Ranh Giới Pha Mặt Trăng</t>
+          <t>Giới Hạn Pha Trăng</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Ánh Sáng Trăng Tròn Nhất</t>
+          <t>Ánh Sáng Trăng Rằm</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Ánh Sáng Rộng Lớn Của Sự Thay Đổi</t>
+          <t>Ánh Sáng Thay Đổi Vô Biên</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Trái Tim Trong Sáng Của Bầu Trời</t>
+          <t>Chinh phục Trái Tim Bầu Trời</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Dòng Chảy Vô Hình Đến Một</t>
+          <t>Dòng Chảy Siêu Nhiên Đến Một</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Abyssal Descent</t>
+          <t>Sa Xuống Vực Sâu</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Journey Together</t>
+          <t>Cùng Nhau Hành Trình</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Blazing Purgatory</t>
+          <t>Luyện Ngục Rực Cháy</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Everburning Flame</t>
+          <t>Ngọn Lửa Cháy Đời</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Cursed Hellfire</t>
+          <t>Hỏa Ngục Bị Nguyền Rủa</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Blade Rinsed, Edge Honed</t>
+          <t>Kiếm Rửa Sạch, Lưỡi Mài bén</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Autumn Waters Severed</t>
+          <t>Dòng Nước Mùa Thu Đứt Đoạn</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Sleeves Stirred, Mist Arising</t>
+          <t>Tà Áo Lay Động, Sương Mù Dâng Trào</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Impending Snow</t>
+          <t>Bão Tuyết Sắp Ðến</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Chờ Để Rút Kiếm</t>
+          <t>Chờ rút vũ khí</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Unraveling Void</t>
+          <t>Giải Thể Hư Không</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Endgame Snip</t>
+          <t>Đoạn Kết Săn</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Infinite Judgment</t>
+          <t>Phán Quyết Vô Biên</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>String Axiom</t>
+          <t>Chân Lý Axiom</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Severance Horizon</t>
+          <t>Chân Trời Đoạn Tuyệt</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Celestial Thunder Master (Self-Claimed)</t>
+          <t>Thiên Lôi Tôn Tự Xưng</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>BIG Thunderclap Talisman</t>
+          <t>Bùa Sấm Sét Cực Đại</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Heavenly Aftershock</t>
+          <t>Thiên Chấn Hậu Sóng</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Evil Spirits, Freeze</t>
+          <t>Linh Hồn Quỷ Dữ, Đông Cứng!</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Divine Augury</t>
+          <t>Điềm Tiên Tri</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>"Lãnh Địa Ngày Hôm Qua"</t>
+          <t>"Lãnh Địa Ngày Xưa"</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Double Neon Colors</t>
+          <t>Màu Neon Kép</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Color Gradient Formula</t>
+          <t>Công Thức Gradient Màu</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Synchronization</t>
+          <t>Đồng Bộ Hóa</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Global Protocol</t>
+          <t>Giao Thức Toàn Cầu</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Iteration</t>
+          <t>Lặp lại và tối ưu</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Closed Loop</t>
+          <t>Vòng Lặp Đóng</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Cascade Reaction</t>
+          <t>Phản Ứng Dây Chuyền</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>The Voyager Star</t>
+          <t>Ngôi Sao Du Hành</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Snowfluff's Song</t>
+          <t>Khúc Ca Bông Tuyết</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Interwoven Starlight</t>
+          <t>Ánh Sao Đan Xen</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Ánh Sáng Cuối Ngôi Sao</t>
+          <t>Ánh Sáng Cuối Cùng Của Ngôi Sao</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Tiếng Vo Ve Xuyên Không Gian</t>
+          <t>Vang Vọng Trong Hư Không</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Till It Dawn Again</t>
+          <t>Cho Đến Bình Minh Mới Lại Lên</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Daybreak Relived</t>
+          <t>Bình Minh Tái Hiện</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Tái Sinh Trong Tĩnh Lặng</t>
+          <t>Tái sinh trong Tĩnh Lặng</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Hướng Đến Ánh Sáng Trong Bóng Tối</t>
+          <t>Tới Ánh Sáng Trong Bóng Tối</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Cơn Mưa Vàng Vĩnh Cửu</t>
+          <t>Mưa Vàng Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Đạt Cấp Độ Liên Kết 10 để mở khóa</t>
+          <t>Đạt Cấp Độ Liên Minh 10 để mở khóa</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Texte de test soumettre l'outil texte 111111</t>
+          <t>Văn bản kiểm tra gửi công cụ 111111</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Texte de test soumettre l'outil texte 1Texte de test soumettre l'outil texte 133333</t>
+          <t>Văn bản kiểm tra gửi công cụ 1Texte de test soumettre l'outil texte 133333</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Nhận nhiệm vụ hàng ngày</t>
+          <t>Nhận nhiệm vụ hàng ngày1</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Translation Text Submission Tool Text 6</t>
+          <t>Công Cụ Nộp Văn Bản Dịch – Văn Bản 6</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>测试文本</t>
+          <t>Văn bản thử nghiệm</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Exploration</t>
+          <t>Thám Hiểm</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Journey</t>
+          <t>Hành Trình</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Battles</t>
+          <t>Trận Chiến</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Voices</t>
+          <t>Những tiếng vọng</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Túi đồ</t>
+          <t>Hành trang</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Exploration: Huanglong</t>
+          <t>Thám hiểm: Huanglong</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Dấu chân ở Hoàng Long I</t>
+          <t>Dấu chân ở Huanglong I</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Dấu chân ở Hoàng Long II</t>
+          <t>Dấu chân ở Huanglong II</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Wilderness Calls</t>
+          <t>Tiếng Gọi Hoang Dã</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Dấu chân trên bờ biển I</t>
+          <t>Dấu chân bên bờ biển I</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Exploration: Rinascita</t>
+          <t>Thám hiểm: Rinascita</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Rover's Journey I</t>
+          <t>Hành Trình Của Rover I</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Huanglong: Borderland City</t>
+          <t>Huanglong: Thành phố Biên Ải</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Những khoảnh khắc bên bạn</t>
+          <t>Khoảnh khắc bên em</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Thế giới muôn màu I</t>
+          <t>Thế giới muôn màu muôn vẻ này</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Rover's Journey II</t>
+          <t>Hành Trình Của Rover II</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Battle Memories</t>
+          <t>Ký Ức Chiến Đấu</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Battle Skills I</t>
+          <t>Kỹ Năng Chiến Đấu I</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Battle Skills II</t>
+          <t>Kỹ Năng Chiến Đấu II</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Unexpected Experience</t>
+          <t>Trải nghiệm bất ngờ</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Battle Skills III</t>
+          <t>Kỹ Năng Chiến Đấu III</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Battle Skills IV</t>
+          <t>Kỹ Năng Chiến Đấu IV</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Con đường trưởng thành</t>
+          <t>Con Đường Trưởng Thành</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Bộ Sưu Tập Echo</t>
+          <t>Thu Thập Tiếng Vọng</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Tidal Scenes</t>
+          <t>Cảnh sắc Thủy Triều</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Cross-Realm Ties</t>
+          <t>Mối Duyên Liên Thế Giới</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Exploration: Lahai-Roi</t>
+          <t>Thám hiểm: Lahai-Roi</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Battle Skills V</t>
+          <t>Kỹ Năng Chiến Đấu V</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Rover's Journey III</t>
+          <t>Hành Trình Của Rover III</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Thế giới muôn màu II</t>
+          <t>Thế Giới Muôn Màu II</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Exploration: Roya Frostlands</t>
+          <t>Thám hiểm: Roya Frostlands</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Ước gì ngọn hải đăng dẫn lối</t>
+          <t>Nguyện Ánh Đèn Hướng Đạo soi sáng ta</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>One-way Road Ahead</t>
+          <t>Đường Một Chiều Phía Trước</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Bắn pháo hoa</t>
+          <t>Bắn pháo hoa lên nào</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>The Metamorphosis</t>
+          <t>Sự Biến Hóa</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Fastest Legend</t>
+          <t>Huyền Thoại Tốc Độ</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Perspective Bender</t>
+          <t>Kẻ Bẻ Cong Góc Nhìn</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Nhảy trong ánh laser</t>
+          <t>Nhảy Múa Trong Ánh Laser</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Cây nấm Roseshoom vs Zombie?</t>
+          <t>Nấm Sầu Đâu vs Thây Ma Hoa Hồng?</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Wild Boar Forest Rampage</t>
+          <t>Cơn Cuồng Nộ Rừng Lợn Rừng</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>The "Ultimate"</t>
+          <t>"Tối Thượng"</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Gấu đến rồi đây</t>
+          <t>Gấu Đến Rồi Đây!</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Just A Rock</t>
+          <t>Chỉ Là Một Hòn Đá</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Though I Can't Fly</t>
+          <t>Dù Tôi Không Thể Bay</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Tình yêu, cái chết &amp; những chiếc xe bị bỏ hoang</t>
+          <t>Tình, Cái Chết &amp; Những Chiếc Xe Bị Bỏ Rơi</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Prism Party</t>
+          <t>Bữa Tiệc Sắc Màu</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Dự Án Ra Mắt của Bộ Ba Lớn!</t>
+          <t>Dự án ra mắt của Tam Đại Cường!</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Giao Thức 3. Tấn Công Loại A!</t>
+          <t>Giao thức 3. Tấn công!</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>An Toàn Là Trên Hết!</t>
+          <t>An Toàn Trên Hết!</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Dọn Sạch Tổ</t>
+          <t>Dọn Tổ</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Starry Hearts</t>
+          <t>Trái Tim Sao Sáng</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Ta Là Kẻ Thách Đấu, Bạn Ơi</t>
+          <t>Ta Là Kẻ Thách Đấu, Người Bạn Ơi</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Honor My Slogan</t>
+          <t>Tôn Vinh Khẩu Hiệu Của Ta</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Remember Me</t>
+          <t>Nhớ Ta Đi</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Days Gone By</t>
+          <t>Những Ngày Đã Qua</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Atom: Jungle's Odyssey</t>
+          <t>Atom: Huyền Thoại Rừng Xanh</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Khi Rừng Không Còn Tối Tăm</t>
+          <t>Khi Rừng Không Còn Tăm Tối</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>A Time Beyond Your Reach</t>
+          <t>Thời Gian Ngoài Tầm Với</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Xin Lỗi, Tôi Là Tuần Tra Viên</t>
+          <t>Xin lỗi, ta là Tuần Tra Viên.</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>A Desperate Gamble</t>
+          <t>Canh Bạc Tuyệt Vọng</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Kẻ Dũng Cảm Chiến Thắng Khi Đường Giao Nhau!</t>
+          <t>Dũng Khí Thắng Khi Đường Giao Nhau!</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Không Có Gì Là Miễn Phí</t>
+          <t>Không gì là miễn phí cả</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Your Mystery, I'll Answer</t>
+          <t>Bí ẩn của ngươi, ta sẽ giải đáp</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Bơi Ra Cho Đến Khi Biển Đổi Xanh</t>
+          <t>Bơi mãi cho đến khi biển hóa xanh</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Full House</t>
+          <t>Thùng Phuy Đầy</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Bậc Thầy Vượt Quá Giới Hạn</t>
+          <t>Bậc Thầy Vượt Tốc</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Đến Đây Nào</t>
+          <t>Đến vì Ya đây</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Soothing Moments</t>
+          <t>Khoảnh Khắc Bình Yên</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Project Clang Bang</t>
+          <t>Dự án Clang Bang</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Reckless Voyager</t>
+          <t>Lữ Khách Bất Cẩn</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Nghỉ Ngơi Một Chút</t>
+          <t>Nghỉ Ngơi Đi</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Launch Control</t>
+          <t>Kiểm soát phóng</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Đã Đến Lúc!</t>
+          <t>Đúng Lúc Rồi Đấy!</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Stress Reliever</t>
+          <t>Bộ Giảm Áp</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Gemberry</t>
+          <t>Quả Gemberry</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Khúc Ballad Của Kiếm</t>
+          <t>Khúc ballad về Kiếm</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Pha Trà Trong Ngày Tuyết Rơi</t>
+          <t>Pha Trà Ngày Tuyết Rơi</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Cầm Cọp Đuôi</t>
+          <t>Mắc Kẹt Với Hổ Dữ</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Phá Bỏ Hàng Rào</t>
+          <t>Phá Vỡ Cái Vảy</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Ferocious Beast</t>
+          <t>Thú Dữ Tợn</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Clang Bang Ice Crusher</t>
+          <t>Ầm Dội Đập Băng</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Wimpy Bug's Nightmare</t>
+          <t>Ác Mộng Của Kẻ Yếu Đuối</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Vượt Qua Lỗi</t>
+          <t>Vượt Qua Bầy Côn Trùng</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Last Puzzle Piece</t>
+          <t>Mảnh Ghép Cuối Cùng</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Snowy Trace</t>
+          <t>Vệt Tuyết</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Lesson Number 5: Live A Bit</t>
+          <t>Bài Học Số 5: Sống Một Chút Đi</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Colors Revived</t>
+          <t>Màu Sắc Hồi Sinh</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Old Family Squab Recipe</t>
+          <t>Công Thức Gia Truyền Nhà Xưa</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Tất cả Maxed Out</t>
+          <t>Đã đạt tối đa</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Quan Sát Đi, Ta Chỉ Thể Hiện Một Lần Thôi!</t>
+          <t>Hãy quan sát đây, ta sẽ chỉ thể hiện một lần duy nhất!</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Into The Darkness</t>
+          <t>Vào Bóng Tối</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Don't Answer That</t>
+          <t>Đừng Có Trả Lời</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Free Solo</t>
+          <t>Đơn Đấu Tự Do</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>"Tôi KHÔNG PHẢI! THẰNG NGU!"</t>
+          <t>"TA KHÔNG PHẢI THẰNG NGU!"</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>And So Sally Can Khoan</t>
+          <t>Và Để Sally Đợi</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Security Essentials</t>
+          <t>Những Điều Cần Biết Về An Ninh</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Ta Đã Gặp Mona Lisa Của Riêng Mình</t>
+          <t>Ta đã gặp được nàng Mona Lisa của đời mình rồi.</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Chơi Bản Piano Trong End of Wandering</t>
+          <t>Chơi bản nhạc piano trong *End of Wandering*</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Cataclysm</t>
+          <t>Tai ương</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>The Perfect Storm</t>
+          <t>Cơn Bão Hoàn Hảo</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Giant Balloon</t>
+          <t>Quả Bóng Khổng Lồ</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Cuộc Chiến Vì Điều Tốt Nhất, Cuộc Chiến Đến Chết</t>
+          <t>Cuộc Chiến Vì Điều Tốt Đẹp Nhất, Cuộc Chiến Đến Chết</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Những Chiếc Chuông, Sự Cô Đơn &amp; Solaris-3</t>
+          <t>Chuông Ngân, Nỗi Cô Đơn &amp; Solaris-3</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Dark Tri-Stars</t>
+          <t>Tam Tinh Hắc Ám</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>A Midsummer Night's Ignis</t>
+          <t>Đêm Hạ Chí Rực Lửa</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Wraith's Melody</t>
+          <t>Khúc nhạc của Wraith</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Bản Giao Hưởng Đêm</t>
+          <t>Giao Hưởng Đêm Tối</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Năm Đêm Tại Plushie's</t>
+          <t>Năm Đêm Kinh Hoàng Của Thú Nhồi Bông</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Your Sun... It's Setting</t>
+          <t>Mặt Trời của ngươi... Đang lặn dần</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Bay Lên Trời Xanh</t>
+          <t>Bay Trên Không Trung</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Chèo Nhanh Lên! Ta Nghe Thấy Tiếng Banjo!</t>
+          <t>Chèo nhanh lên! Tao nghe thấy tiếng đàn banjo rồi!</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>The Kite Rider</t>
+          <t>Kỵ Sĩ Diều Bay</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Freehand Circle</t>
+          <t>Vòng Tròn Tự Do</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Don't Frate About It</t>
+          <t>Đừng Có Lo</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Tại Sao Con Quạ Giống Cái Bàn Viết?</t>
+          <t>Tại Sao Quạ Lại Giống Cái Bàn Viết</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>The Lifer's Salvation</t>
+          <t>Sự Cứu Rỗi Của Kẻ Sống Sót</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Giới Hạn Của Trí Tuệ</t>
+          <t>Giới hạn Trí Tuệ</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>The Storm That Is Approaching</t>
+          <t>Cơn Bão Đang Đến Gần</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Cánh Cổng Averardo</t>
+          <t>Cổng Averardo</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Swim Up</t>
+          <t>Bơi Lên</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Blind Spot</t>
+          <t>Điểm Mù</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Mặt Trời Và Sáu Đồng Vàng</t>
+          <t>Mặt Trời và Sáu Đồng Vàng</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>It Takes Two</t>
+          <t>Cần Có Hai Người</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Way Out</t>
+          <t>Lối Thoát</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Băng Qua Cầu Vồng</t>
+          <t>Qua Những Dải Cầu Vồng</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>The Skyfire</t>
+          <t>Lửa Trời</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>The Fool's Pathway</t>
+          <t>Con Đường Của Kẻ Ngốc</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Gondola Elevator</t>
+          <t>Thang máy Gondola</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Biển Hoa Cần Một Bờ</t>
+          <t>Biển Hoa Cần Bờ Bến</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Lost Glory</t>
+          <t>Vinh Quang Lạc Lối</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Crimson Twilight</t>
+          <t>Chạng Vạng Đỏ Lệ</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Bay Lên Nào!</t>
+          <t>Lên Nào!</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Auto Handpuppet</t>
+          <t>Bù nhìn tự động</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Phù Thủy Trong Đêm Linh Thiêng</t>
+          <t>Phù Thủy Đêm Thánh</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Deadly Ballet</t>
+          <t>Vũ Điệu Tử Thần</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Hiệp Sĩ Trong Cơn Bão</t>
+          <t>Hiệp Sĩ Trong Bão Tố</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Dream Guardian</t>
+          <t>Người Bảo Vệ Giấc Mơ</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>The Wind Ends Here</t>
+          <t>Gió Dừng Lại Ở Đây</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Chiếc Nhẫn Của Kẻ Sống Sót</t>
+          <t>Nhẫn Của Kẻ Sống Sót</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>We're Tất cả Alone</t>
+          <t>Chỉ còn lại chúng ta thôi.</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Plushie Village</t>
+          <t>Làng Thú Nhồi Bông</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Graffiti Artist</t>
+          <t>Nghệ Sĩ Vẽ Graffiti</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Bóng Tối Của Những Tòa Tháp</t>
+          <t>Bóng Tối Những Tòa Tháp</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>The Maiden Candidate</t>
+          <t>Ứng Cử Viên Thánh Nữ</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Cuộc Chinh Phục Của Ta Là Biển Sao</t>
+          <t>Cuộc Chinh Phục Biển Sao của ta</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Thessaleo Wonder</t>
+          <t>Kỳ Quan Thessaleo</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Kỳ Nghỉ Của Ragunna</t>
+          <t>Kỳ Nghỉ Ragunna</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>The Seven Deadly Sins</t>
+          <t>Thất Đại Tội Ác</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>I'd Win</t>
+          <t>Tôi sẽ thắng thôi.</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Khoảnh Khắc Này Là Của Riêng Ngươi</t>
+          <t>Khoảnh Khắc Này Là Của Ngươi Để Gìn Giữ</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Human Wind Tamer</t>
+          <t>Kẻ Thuần Hóa Gió Loài Người</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Treasure Hunter</t>
+          <t>Thợ Săn Kho Báu</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>The Treasure Trail</t>
+          <t>Con Đường Kho Báu</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Take Your Heart</t>
+          <t>Hãy Theo Đuổi Trái Tim Mình</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>It Is Written</t>
+          <t>Đã Được Định Sẵn</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Ở Đây Tối Và Đáng Sợ Quá!</t>
+          <t>Nơi này tối tăm và đáng sợ quá!</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>"I Must Break Bạn"</t>
+          <t>"Ta phải đập tan ngươi."</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Hầu Như Không Phải Phán Quyết Cuối Cùng</t>
+          <t>Khó lòng là Phán Quyết Cuối Cùng</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Hầu Như Không Phải Tuyên Bố Cuối Cùng</t>
+          <t>Khó lòng là Tuyên Ngôn Cuối Cùng</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Những Con Rồng Bên Cạnh</t>
+          <t>Nhà Bên Cạnh Drake</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Air Superiority</t>
+          <t>Ưu Thế Trên Không</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Vinh Quang Dành Cho Kẻ Lang Thang</t>
+          <t>Vinh Quang cho Kẻ Lang Thang!</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Cánh Cổng Của Kỷ Nguyên Mới</t>
+          <t>Những Cánh Cổng Của Kỷ Nguyên Mới</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Không More Cages</t>
+          <t>Không Còn Lồng Nhốt</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Di Chuyển Đi, Những Bức Tượng!</t>
+          <t>Di chuyển đi, tượng kia!</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Ta Đang Ở Đ*u Đâu Thế?</t>
+          <t>Tao đang ở cái chỗ quái quỷ nào thế này?</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Hãy Để Bầu Trời Xanh Được Biết Đến</t>
+          <t>Hãy để Bầu Trời Xanh được biết đến</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Dù Thời Gian Trôi Qua</t>
+          <t>Dù thời gian trôi qua</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Luôn Có Một Thử Thách Khác</t>
+          <t>Thử Thách Không Bao Giờ Dứt</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Nhìn Đống Gulpuff Kia Kìa...</t>
+          <t>Nhìn Bao Nhiêu Gulpuff Kìa...</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Plushie Story</t>
+          <t>Câu Chuyện Bông Gòn</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Rover Inverted</t>
+          <t>Vận Mệnh Giả - Phản Chiều</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Ước Gì Trên Những Vì Sao</t>
+          <t>Ước Giữa Ngàn Sao</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>BEWARE OF SCAMMERS</t>
+          <t>CẢNH GIÁC KẺ LỪA ĐẢO</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Chests "R" Us</t>
+          <t>Rương "R" Us</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Artistic Attainments</t>
+          <t>Thành Tựu Nghệ Thuật</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Bộ Não Rộng Lớn Hơn Bầu Trời</t>
+          <t>Bộ Não Rộng Hơn Bầu Trời</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Grand Tour</t>
+          <t>Hành Trình Vĩ Đại</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Dùng "Cánh Cổng Đoàn Kết" để dịch chuyển một lần</t>
+          <t>Dùng "Cánh Cửa Đoàn Kết" để dịch chuyển một lần</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Hãy Lao Xuống. Ngươi Sẽ Không Chết Đâu.</t>
+          <t>Hãy nhảy xuống đi. Cậu sẽ không chết đâu.</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Passionate Gladiator</t>
+          <t>Đấu Sĩ Nồng Nhiệt</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>I Abandon Here My Happiness</t>
+          <t>Ta Bỏ Lại Nơi Đây Niềm Hạnh Phúc</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Vượt Qua Điểm Không Thể Quay Lại</t>
+          <t>Vượt Qua Giới Hạn Không Thể Quay Lại</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Ba Bức Tường Ư? Ba Thành Tựu!</t>
+          <t>Ba bức tường? Ba thành tựu!</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Nó Giống Như Một Ngọn Hải Đăng Trong Tay Ngươi</t>
+          <t>Như Ngọn Hải Đăng Trong Tay Bạn</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Many Foes, One Strike</t>
+          <t>Nhiều Kẻ Thù, Một Đòn Quyết Định</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Một Nhát Chém, Trong Vô Số Nhát Chém</t>
+          <t>Một Lưỡi Dao, Trong Vô Số</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>RISE</t>
+          <t>ĐỨNG LÊN</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>To Your Radiant Eternity</t>
+          <t>Dành Tặng Sự Vĩnh Hằng Rực Rỡ Của Người</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Destined Death</t>
+          <t>Cái Chết Định Mệnh</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>12 Imprisoned Men</t>
+          <t>12 Những Người Bị Giam Cầm</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>I Feel Like I'm Flying</t>
+          <t>Ta cảm giác như đang bay vậy.</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>The Unseen World</t>
+          <t>Thế Giới Vô Hình</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>The Horn That Never Dies</t>
+          <t>Tiếng Kèn Bất Tử</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Sun That Never Sets</t>
+          <t>Mặt Trời Không Bao Giờ Lặn</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Presage Flower</t>
+          <t>Hoa Tiên Tri</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Buried Wonder</t>
+          <t>Kỳ Quan Vùi Lấp</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Celestial Magician</t>
+          <t>Pháp Sư Bầu Trời</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Đội Bông Nhồi Bông, Trở Lại Huy Hoàng!</t>
+          <t>Đội Bông Gòn, Trở Lại Huy Hoàng!</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Thần Tính Của Septimont</t>
+          <t>Thần Tính của Septimont</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Cậu Bé Fusion Và Cô Gái Glacio</t>
+          <t>Cậu Bé Hợp Nhất và Cô Gái Băng Giá</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Death Smiles At Us Tất cả</t>
+          <t>Tử Thần Mỉm Cười Với Ta</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Ánh Sáng, Bóng Tối, Cả Hai Đều Có Thể Chặt Đứt</t>
+          <t>Ánh Sáng hay Bóng Tối, đều có thể bị chém đứt</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Hai Cõi Như Một</t>
+          <t>Hai Vòm Trời Hợp Nhất</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Kerasaur Tears</t>
+          <t>Nước Mắt Kerasaur</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Đánh Bại Kerasaurs Bị Mắc Kẹt Tại Titanbone Expanse</t>
+          <t>Tiêu diệt bọn Kerasaur bị mắc kẹt trên Titanbone Expanse</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Hoàn Thành Thử Thách Thu Thập Torn Pages Tại Border Mountains</t>
+          <t>Hoàn thành thử thách Bộ sưu tập Trang Giấy Rách tại Dãy Núi Biên Giới</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Shadow Under Spotlight</t>
+          <t>Bóng Dưới Ánh Đèn</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>City That Shines</t>
+          <t>Thành Phố Rực Rỡ</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Yesterday Glory Once More</t>
+          <t>Hôm qua, một lần nữa rực rỡ</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Trong Mùa Tang Thương</t>
+          <t>Mùa Thương Khóc</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Máu Và Mặt Trời</t>
+          <t>Máu và Mặt Trời</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Unwithering Flower</t>
+          <t>Bông Hoa Bất Diệt</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Nốt Kết, Nốt Khởi Đầu</t>
+          <t>Ghi Chú Kết Thúc, Ghi Chú Bắt Đầu</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Where Yesterday Waits</t>
+          <t>Nơi Ngày Hôm Qua Đợi Chờ</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Về Vũ Khí Và Con Người Ta Ngâm Ca</t>
+          <t>Khúc Ca Về Vũ Khí Và Con Người</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Nhịp Tim Khiêu Vũ Trong Bóng Tối</t>
+          <t>Nhịp Tim Nhảy Múa Trong Bóng Tối</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>May Flames Guide Bạn</t>
+          <t>Ngọn Lửa Dẫn Lối Cho Ngươi</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Happy Hunting</t>
+          <t>Chúc săn bắn vui vẻ</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>A Spark Passed On</t>
+          <t>Ngọn Lửa Được Truyền Lại</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Till We Meet Again</t>
+          <t>Cho Đến Khi Ta Gặp Lại</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Màu Của Bình Minh</t>
+          <t>Sắc Bình Minh</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Where Paradise Starts Journeying</t>
+          <t>Nơi Thiên Đường Bắt Đầu Hành Trình</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Một Chú Thích Khác Của Hành Trình</t>
+          <t>Một Chú Giải Khác trên Hành Trình</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Summertime, Warm Lights, Homeward Path</t>
+          <t>Mùa Hè, Ánh Đèn Ấm, Lối Về Nhà</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Gánh Nặng Của Thế Gian</t>
+          <t>Gánh Nặng Thế Gian</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Ngày Tận Thế Và Một Quán Cà Phê</t>
+          <t>Tận Thế và Một Quán Cà Phê</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Những Điều Bạn Có Thể Và Không Thể Làm</t>
+          <t>Những Gì Bạn Có Thể Và Không Thể Làm</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Amber-Preserved Faith</t>
+          <t>Niềm Tin Hổ Phách</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Đừng Hiền Lành Đi Vào Đêm Đẹp Đẽ Ấy</t>
+          <t>Đừng Lặng Lẽ Tan Vào Đêm Đẹp Đẽ Đó</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>The Story Bạn Don't Know</t>
+          <t>Câu Chuyện Ngươi Chưa Biết</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Ngươi, Ánh Sao Lấp Lánh</t>
+          <t>Ngươi, Ánh Sao Băng</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Cẩm Nang Du Hành cho Kẻ Đi Nhờ đến Lahai-Roi</t>
+          <t>Cẩm nang đi nhờ tàu đến Lahai-Roi</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Hello, Motor</t>
+          <t>Chào cậu, Motor.</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Đi Trong Bóng Tối</t>
+          <t>Bước Trong Bóng Tối</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Silent Mode</t>
+          <t>Chế Độ Vô Thanh</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Hướng Tới Thế Giới Mới</t>
+          <t>Tới Thế Giới Mới</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Iridescent Rain</t>
+          <t>Mưa Irideglow</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>A New Dawn</t>
+          <t>Bình Minh Mới</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Trở Lại Khuôn Viên</t>
+          <t>Trở lại Khu Học Xá</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Steady Toward Destiny</t>
+          <t>Vững bước về Định Mệnh</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Đứa Con Của Ánh Sáng</t>
+          <t>Đứa trẻ của Ánh Sáng</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>RPG Master</t>
+          <t>Bậc Thầy RPG</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Cực Điểm Của Solaris</t>
+          <t>Cực Địa Solaris</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Spring Has Come</t>
+          <t>Xuân Đã Về</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>The Long Fall</t>
+          <t>Cú Rơi Dài</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Home Sweet Home</t>
+          <t>Ngôi Nhà Thân Yêu</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Dear Giovanni</t>
+          <t>Gửi Giovanni thân mến,</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Rock-Paper-Scissors Pro</t>
+          <t>Bậc thầy Oẳn Tù Tì</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Nivora's Pinecone</t>
+          <t>Quả Thông của Nivora</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Làm Thế Nào Để Thoát Khỏi Cái Bóng Của Mình?</t>
+          <t>Làm Sao Để Vứt Bỏ Bóng Tối?</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>The Three Students</t>
+          <t>Ba Học Sinh</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>...Will Soon Fade Out</t>
+          <t>...Sẽ sớm tan biến thôi</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>The Azure Echoes</t>
+          <t>Những Âm Thanh Xanh</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Teenager Not In Wonderland</t>
+          <t>Thiếu Niên Ngoài Xứ Thần Tiên</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Another</t>
+          <t>Lại nữa à...</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Drawer And A Time Machine</t>
+          <t>Ngăn Kéo Và Cỗ Máy Thời Gian</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Siggy's Gem</t>
+          <t>Viên ngọc của Siggy</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>The Danger Within</t>
+          <t>Hiểm Họa Bên Trong</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Ta... Là Ai?</t>
+          <t>Ta... ta là ai?</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Bờ Cõi Cứu Rỗi Xa Nhất</t>
+          <t>Bờ Vực Cứu Rỗi Cuối Cùng</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>A Savior Is Mọi người</t>
+          <t>Vị Cứu Tinh Của Mọi Người</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>The Bell Still Rings</t>
+          <t>Tiếng Chuông Vẫn Còn Vang</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Đưa Em Đến Với Mặt Trăng</t>
+          <t>Đưa ta đến Mặt Trăng</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Farewell, Waking Hunter</t>
+          <t>Tạm biệt, Kẻ Săn Thức.</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Khúc Ca Carnevale</t>
+          <t>Khúc Ca Carnival</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Sự Trở Lại Của Bình Minh</t>
+          <t>Sự trở lại của Ánh Bình Minh</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>The Stars Still Burn Bright</t>
+          <t>Những Vì Sao Vẫn Rực Cháy</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>From Now Till Sunrise</t>
+          <t>Từ Giờ Đến Bình Minh</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Khi Bầu Trời Mang Màu Mắt Em</t>
+          <t>Khi Bầu Trời Mang Màu Mắt Anh</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Sakura, Nhìn Từ Bên Cạnh Hay Từ Dưới Lên?</t>
+          <t>Sakura – Nhìn Từ Bên Cạnh Hay Từ Dưới Lên?</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Mysterious Scissorswoman</t>
+          <t>Kẻ Cắt Xén Bí Ẩn</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Bright Star</t>
+          <t>Ngôi Sao Sáng</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Hôm nay's Weather: Sunny</t>
+          <t>Thời tiết hôm nay: Nắng</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Moonlite Echoes</t>
+          <t>Tiếng Vọng Trăng Sáng</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Those Bạn Protected</t>
+          <t>Những người mà cậu đã bảo vệ</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>The Perfect Teatime</t>
+          <t>Giờ Trà Hoàn Hảo</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Memory Catcher</t>
+          <t>Bắt Giữ Ký Ức</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Như một cánh chim...</t>
+          <t>Như một chú chim...</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>A Tiny Palm</t>
+          <t>Bàn Tay Nhỏ Bé</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Đỏ Rực Trong Tuyết</t>
+          <t>Lửa Đỏ Trong Tuyết</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Chuyến Tàu Đến Những Ngày Xuân</t>
+          <t>Hành Trình Ngày Xuân</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Sau khi Snow Melts</t>
+          <t>Sau Khi Tuyết Tan</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Hoa Dâm Bụt Lúc Chạng Vạng</t>
+          <t>Hoa Dâm Bụt Hoàng Hôn</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Tiếng Vỗ Tay Nơi Hoang Dã</t>
+          <t>Tiếng Vỗ Tay Hoang Dã</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Võ Sĩ Quyết Tâm Hy Sinh</t>
+          <t>Một Võ Sĩ Quyết Định Chết</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Hướng Đến Ngày Mai Không Bao Giờ Tàn Phai</t>
+          <t>Tới Ngày Mai Không Bao Giờ Tàn Phai</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Legends Never Fade</t>
+          <t>Huyền Thoại Không Bao Giờ Phai Mờ</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Chuyến Đi Cuối Cùng Trong Ngày</t>
+          <t>Chuyến Đi Cuối Ngày</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Bài Ca Dành Cho Kẻ Chiến Thắng</t>
+          <t>Khúc hát Chiến Thắng</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Gửi Những Người Đã Ra Đi</t>
+          <t>Tưởng Nhớ Những Người Đã Khuất</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Endorsement Fulfilled</t>
+          <t>Đã Hoàn Thành Chứng Thực</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Quả Táo và Em</t>
+          <t>Táo và Cậu</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Street Where Wind Resides</t>
+          <t>Con Đường Gió Ngự</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Mirror, Mirror</t>
+          <t>Gương kia ngự ở trên tường...</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Where Lone Wolf Resides</t>
+          <t>Nơi Sói Cô Đơn Trú Ngụ</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Giữa Nơi Đây và Vùng Kia</t>
+          <t>Giữa Nơi Đây và Viễn Xứ</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Giai Điệu Ngày Xưa</t>
+          <t>Khúc Nhạc Ngày Xưa</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Mọi Con Đường Đều Dẫn Đến Ta</t>
+          <t>Mọi Con Đường Dẫn Đến Ta</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Radiant Time</t>
+          <t>Thời Gian Rạng Ngời</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>The Legend Ain't Over Yet</t>
+          <t>Huyền Thoại Vẫn Chưa Kết Thúc</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Chiến Đấu Hết Mình Là Danh Dự</t>
+          <t>Chiến Đấu Hết Mình Là Tôn Vinh</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Con Gái Của Biển Cả</t>
+          <t>Con Gái Biển Cả</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Familiar Stranger</t>
+          <t>Người Lạ Quen Thuộc</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Công Dân Hữu Ích</t>
+          <t>Công Dân Tốt Bụng</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Reap What Bạn Sow</t>
+          <t>Gieo Nhân Nào Gặt Quả Nấy</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Cậu Giỏi Mở Cửa Sổ Quá</t>
+          <t>Cậu giỏi mở cửa sổ nhỉ</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Taste Buds Tickles</t>
+          <t>Vị giác rộn ràng</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Trẻ Trung Trong Tâm Hồn</t>
+          <t>Trẻ Lòng</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>DIY Hướng dẫn</t>
+          <t>Hướng Dẫn Tự Chế</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Leng Keng, Cạch Cạch!</t>
+          <t>Cạch, cạch, keng!</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Kẻ Mang Ánh Sáng</t>
+          <t>Người Mang Ánh Sáng</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>For Divinity Took Him</t>
+          <t>Vì Người Đã Được Thần Linh Đón Nhận</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Khúc Ca Từ Giấc Mơ Đã Mất</t>
+          <t>Khúc Ru Từ Giấc Mơ Lạc Lối</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Express Delivery</t>
+          <t>Giao Hàng Nhanh</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Di Vật Này Dành Cho Ngươi</t>
+          <t>Di Vật này dành cho cậu đấy</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Hỏi Thì Sẽ Nhận Được</t>
+          <t>Hỏi đi rồi sẽ có câu trả lời.</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Một Câu Trả Lời Khác Cho Sự Hủy Diệt</t>
+          <t>Lời Đáp Khác cho Sự Hủy Diệt</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>The Star Bạn Once Sought</t>
+          <t>Ngôi Sao Mà Ta Từng Theo Đuổi</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Black Cat Sensei</t>
+          <t>Sư Phụ Mèo Đen</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Nói chuyện với chú mèo đen bí ẩn tại Ngã Tư Honami</t>
+          <t>Nói chuyện với chú mèo đen bí ẩn ở Ngã tư Honami</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>When Supernatural Confessions Became Commonplace</t>
+          <t>Khi Những Lời Thú Tội Siêu Nhiên Trở Thành Điều Bình Thường</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Honami's Greatest Detective</t>
+          <t>Thám Tử Vĩ Đại Nhất Của Honami</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Bằng Chứng Về Sự Tồn Tại Của Cô Ấy</t>
+          <t>Bằng Chứng Tồn Tại Của Cô Ấy</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Càng Gần Nhà, Lòng Càng Rụt Rè</t>
+          <t>Càng gần nhà, lòng càng rụt rè</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Bông Hoa Chúng Ta Đã Thấy Hôm Ấy</t>
+          <t>Bông Hoa Ta Thấy Hôm Ấy</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Heartfelt Words</t>
+          <t>Lời Chân Thành</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Unfinished Chụp ảnh Album</t>
+          <t>Album ảnh dở dang</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Every Ordinary Ngày We've Shared</t>
+          <t>Mỗi Ngày Bình Thường Ta Đã Chung Lối</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Đã Từng Lạc Lối, Nay Đã Tìm Thấy</t>
+          <t>Từng Lạc Lối, Nay Đã Tìm Thấy</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Urgent Aid</t>
+          <t>Hỗ Trợ Khẩn Cấp</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Apocalypse Camp</t>
+          <t>Trại Tận Thế</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Laid-Quay lại Expedition</t>
+          <t>Cuộc Thám Hiểm Thư Thái</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Khúc Gian Tấu Của Nhịp Tim</t>
+          <t>Khúc Tạm Ngừng Của Nhịp Tim</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Alone Among Stars</t>
+          <t>Một Mình Giữa Ngàn Sao</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Eternal Among Stars</t>
+          <t>Vĩnh Hằng Giữa Ngân Hà</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Tái Sinh Trong Cái Chết</t>
+          <t>Tái sinh trong Cái Chết</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Khi Những Cơn Gió Ngừng Thổi</t>
+          <t>Khi Gió Ngừng Thổi</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Trước Khi Những Cơn Gió Thổi</t>
+          <t>Trước khi Gió Thổi Qua</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Not A Checkpoint</t>
+          <t>Không Phải Điểm Kiểm Tra</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Take On Me</t>
+          <t>Đến lượt ta</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Fully Flavored</t>
+          <t>Vị Đậm Đà Trọn Vẹn</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Một Lỗ Hổng Được Định Nghĩa Bởi Đường Thẳng</t>
+          <t>Lỗ Hổng Định Hình Bởi Đường Thẳng</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>The Forgotten Insulindian</t>
+          <t>Người Insulindian Bị Lãng Quên</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Weather Simulation Ready</t>
+          <t>Mô Phỏng Thời Tiết Sẵn Sàng</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>A Great Tragedy</t>
+          <t>Bi Kịch Vĩ Đại</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Ít Nhất Ngươi Vẫn Còn Nhớ...</t>
+          <t>Ít Nhất Ngươi Còn Nhớ...</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Không Theo Kịp Fitz…</t>
+          <t>Không theo kịp Fitz rồi…</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>My Motor Arrives</t>
+          <t>Xe Của Ta Đã Đến</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Ta Có Nên Treo Bít Tất Không?</t>
+          <t>Có Nên Treo Bít Tất Không Nhỉ?</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Ice Swimmer</t>
+          <t>Kình Ngư Băng</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>The Victory Bạn Witnessed</t>
+          <t>Chiến Thắng Mà Ngươi Chứng Kiến</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Tuân Theo Quy Trình</t>
+          <t>Tuân theo Quy Trình</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Làm Theo Trái Tim</t>
+          <t>Hãy nghe theo trái tim mình</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Slip Carefully</t>
+          <t>Cẩn thận trơn trượt</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Delighting Bạn Always</t>
+          <t>Luôn Làm Bạn Hài Lòng</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Chúng Nở Trong Đêm</t>
+          <t>Chúng Nở Trong Bóng Đêm</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Sau Khi Chúng Nở Trong Đêm</t>
+          <t>Sau Khi Chúng Nở Đêm Đen</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Điểm Cuối Của Tuyến Tuyết</t>
+          <t>Biên Giới Tuyết Tan</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Dưới Bầu Trời Xanh Coban</t>
+          <t>Dưới Bóng Coban</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Knock Knock</t>
+          <t>Cốc Cốc</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Chú Mèo và Bậc Thầy Trốn Tìm</t>
+          <t>Mèo và Bậc Thầy Trốn Tìm</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Một Cô Gái Có Thể Làm Gì Được Chứ?</t>
+          <t>Một cô gái có thể làm được gì chứ?</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Trợ lý Ấp Trứng Spacetrek</t>
+          <t>Trợ lý Ấp trứng Spacetrek</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Second Author</t>
+          <t>Tác Giả Thứ Hai</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Dimmr Plains Observer</t>
+          <t>Quan Sát Viên Đồng Bằng Dimmr</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Apprentice Pouchmaker</t>
+          <t>Thợ Làm Túi Tập Sự</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Electric Touch</t>
+          <t>Xúc Giác Điện</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Remember Me</t>
+          <t>Nhớ Ta Đi</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Side Hustle Guidance</t>
+          <t>Hướng dẫn Kiếm thêm ngoài giờ</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Câu Chuyện Cuộc Đời Của Chuu</t>
+          <t>Hành Trình Cuộc Đời Chuu</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Nó Giống Như Một Ngọn Hải Đăng Trong Tay Bạn</t>
+          <t>Như Ngọn Hải Đăng Trong Tay Bạn</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Absolute Anchor Field</t>
+          <t>Trường Neo Tuyệt Đối</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Flame-Illuminated Trail</t>
+          <t>Lối Đi Ánh Lửa</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Unkindled Ember</t>
+          <t>Ngọn Lửa Tàn Phai</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Wootter, We Found Bạn</t>
+          <t>Wootter, chúng tớ tìm thấy cậu rồi!</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Trong Ngôi Nhà Vĩnh Hằng, Đợi Chờ Giấc Mơ.</t>
+          <t>Nơi Nhà Vĩnh Hằng, Giấc Mơ Đợi Chờ.</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Dragon's Homecoming</t>
+          <t>Rồng Trở Về</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Gặp Gỡ Scourgewings Iaen và Isth Tại Cao Nguyên Sanguis</t>
+          <t>Đối đầu Scourgewings Iaen và Isth tại Cao nguyên Sanguis</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Bird Without Legs</t>
+          <t>Chim Không Chân</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Nàng Nhớ Về Những Ngọn Lửa</t>
+          <t>Cô Nhớ Về Ngọn Lửa</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Immortal Severance</t>
+          <t>Phân Thân Bất Diệt</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Yesterday's Battle Marks</t>
+          <t>Dấu vết trận chiến hôm qua</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Don't Panic</t>
+          <t>Đừng Hoảng Loạn</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
